--- a/data/DOC-06-danh-sach-nhan-su.xlsx
+++ b/data/DOC-06-danh-sach-nhan-su.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân sự" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đã nghỉ việc" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,14 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001E7D32"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C62828"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,16 +91,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,1690 +464,2097 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Mã phòng ban</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phòng ban</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Chức danh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Mã NV</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Họ tên</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Chức danh</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Phòng ban</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ngày vào</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ngày nghỉ</t>
+          <t>Quản lý trực tiếp</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Ngày vào làm</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Lương (VND)</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lương</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tổng Giám đốc (CEO)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>NV-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Văn An</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Tổng Giám đốc (CEO)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>01/03/2019</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>60000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Trợ lý Tổng Giám đốc</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>NV-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Đỗ Thị Lan</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Trợ lý Tổng Giám đốc</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>15/06/2020</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>26000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Hành chính</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>NV-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Hoàng Minh Tuấn</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Hành chính</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>02/01/2021</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Pháp chế</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>NV-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Phan Thị Thu</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Pháp chế</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>10/09/2021</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên IT nội bộ</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>NV-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Lê Quốc Dũng</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên IT nội bộ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>05/04/2022</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>18000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Lái xe</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>NV-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Trần Văn Hùng</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Lái xe</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>12/07/2019</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Lễ tân</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>NV-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Thị Hoa</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Lễ tân</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>03/02/2023</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Bảo vệ</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>NV-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Bùi Đức Mạnh</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Bảo vệ</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>20/08/2020</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
         <v>9000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>NV-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Vũ Thị Nga</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Thủ quỹ</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18/11/2021</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Hành chính</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Mua hàng</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>NV-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Đặng Văn Thành</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Mua hàng</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>09/05/2022</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>17000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Giám đốc Tài chính (CFO)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>NV-011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Trần Thị Minh</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Giám đốc Tài chính (CFO)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>55000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán trưởng</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>NV-012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Ngô Thị Bích</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán trưởng</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>15/02/2020</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>38000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán tổng hợp</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>NV-013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Lý Văn Khoa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán tổng hợp</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>08/08/2021</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán công nợ</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>NV-014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Phạm Thị Yến</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán công nợ</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
         <v>16000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán thuế</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>NV-015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Trịnh Văn Long</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán thuế</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>22/06/2021</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>17000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán kho</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>NV-016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Hồ Thị Duyên</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán kho</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>30/09/2022</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Phân tích tài chính</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>NV-017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Đoàn Minh Khôi</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Phân tích tài chính</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>05/01/2023</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>23000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tài chính — Kế toán</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Kế toán thanh toán</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>NV-018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Cao Thị Ngọc</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Kế toán thanh toán</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>NV-011</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>14/10/2023</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Giám đốc Kinh doanh (Sales Director)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>NV-019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Lê Hoàng Giang</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Giám đốc Kinh doanh (Sales Director)</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>01/05/2019</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
         <v>50000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Trưởng nhóm Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>NV-020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Thị Thủy</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Trưởng nhóm Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>12/03/2020</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>NV-021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Trần Văn Nam</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>20/07/2021</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
         <v>16000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>NV-022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Phạm Văn Sơn</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>03/09/2021</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>NV-023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Vũ Thị Hương</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>15/01/2022</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>NV-024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Đinh Văn Phúc</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>28/04/2022</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Chăm sóc KH</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>NV-025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Bùi Thị Linh</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Chăm sóc KH</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>10/06/2022</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>NV-026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Lương Văn Tài</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>19/08/2022</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Chăm sóc KH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>NV-027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Hà Thị Trang</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Chăm sóc KH</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>07/11/2022</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>NV-028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Trương Văn Bình</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>02/02/2023</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>NV-029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Văn Đạt</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kinh doanh</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>16/05/2023</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Kinh doanh</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Chăm sóc KH</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>NV-030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Phan Thị Mai</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Chăm sóc KH</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>NV-019</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>21/09/2023</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Trưởng phòng Vận hành (Ops Lead)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>NV-031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Vũ Đức Thắng</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Trưởng phòng Vận hành (Ops Lead)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>01/06/2019</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
         <v>32000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Giám sát Kho</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>NV-032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Văn Kiên</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Giám sát Kho</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>14/02/2020</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
         <v>18000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kho</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>NV-033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Trần Thị Hồng</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kho</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>09/07/2021</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Giao nhận</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>NV-034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Lê Văn Toàn</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Giao nhận</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>22/09/2021</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Giao nhận</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>NV-035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Phạm Văn Lộc</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Giao nhận</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>05/01/2022</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ thuật viên Bảo trì</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>NV-036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Đỗ Văn Hải</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ thuật viên Bảo trì</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ thuật viên Bảo trì</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>NV-037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Ngô Văn Tân</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ thuật viên Bảo trì</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>27/06/2022</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Điều phối Vận hành</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>NV-038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Hoàng Thị Vân</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Điều phối Vận hành</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>11/10/2022</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kho</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>NV-039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Bùi Văn Quang</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Kho</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>03/03/2023</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Giao nhận</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>NV-040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Trần Văn Lâm</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Giao nhận</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>19/07/2023</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Nhân sự</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Trưởng phòng Nhân sự (HR Manager)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>NV-041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Phạm Thị Hạnh</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Trưởng phòng Nhân sự (HR Manager)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
         <v>30000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Nhân sự</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Tuyển dụng</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>NV-042</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Nguyễn Thị Diệu</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Tuyển dụng</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>NV-041</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>12/04/2020</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
         <v>16000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Nhân sự</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên C&amp;B</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>NV-043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Lê Thị Oanh</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên C&amp;B</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>NV-041</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>08/08/2021</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
         <v>17000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Nhân sự</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Đào tạo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>NV-044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Trần Văn Hoàng</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Chuyên viên Đào tạo</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>NV-041</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>15/02/2022</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Nhân sự</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Hành chính Nhân sự</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>NV-045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Vũ Thị Kim</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Nhân viên Hành chính Nhân sự</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>NV-041</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>20/06/2023</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NV-046</t>
+          <t>CUS</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Phú</t>
+          <t>Kinh doanh</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2166,230 +2564,417 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CUS</t>
+          <t>NV-052</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>10/03/2021</t>
+          <t>Mai Văn Lực</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>TERMINATED</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n">
+          <t>NV-999</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kho</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>NV-053</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Tạ Thị Hiền</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>NV-031</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>15/13/2026</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Phòng Marketing</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên viên Marketing</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>NV-054</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Kiều Văn Tú</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>NV-001</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>16000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mã NV</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Chức danh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Phòng ban</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ngày vào</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ngày nghỉ</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Lương</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NV-046</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Phú</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nhân viên Kinh doanh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CUS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10/03/2021</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>NV-047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lê Thị Hạnh</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Kế toán kho</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FIN</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>22/07/2020</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>31/01/2026</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TERMINATED</t>
         </is>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="H3" t="n">
         <v>13000000</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>NV-048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Trần Văn Kỳ</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Nhân viên Giao nhận</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>05/05/2022</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TERMINATED</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H4" t="n">
         <v>11000000</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>NV-049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Phạm Thị Nhung</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Chuyên viên Chăm sóc KH</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CUS</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>18/09/2021</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TERMINATED</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H5" t="n">
         <v>12000000</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>NV-050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Đỗ Văn Chung</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Chuyên viên IT nội bộ</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12/01/2020</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TERMINATED</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H6" t="n">
         <v>18000000</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>NV-051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Vũ Thị Lệ</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Chuyên viên Tuyển dụng</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>03/11/2022</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TERMINATED</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H7" t="n">
         <v>15000000</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Tổng quỹ lương tháng (ACTIVE) = 855.000.000 đ</t>
         </is>
